--- a/web/templates/Project5/David_version/09_RT-qPCR_data.xlsx
+++ b/web/templates/Project5/David_version/09_RT-qPCR_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haixi\Documents\DataHarmonizerDevelop\web\templates\Project5\David_version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38ED6BCF-ACA9-4347-886A-5DDEAB1FBF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42665624-48E3-4246-A8F8-13B9ADA6E987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D186E85A-2681-487D-9322-615EB35A29E6}"/>
   </bookViews>

--- a/web/templates/Project5/David_version/09_RT-qPCR_data.xlsx
+++ b/web/templates/Project5/David_version/09_RT-qPCR_data.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haixi\Documents\DataHarmonizerDevelop\web\templates\Project5\David_version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42665624-48E3-4246-A8F8-13B9ADA6E987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1344877B-2F7B-4F7A-8719-906E3FF78560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D186E85A-2681-487D-9322-615EB35A29E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{D186E85A-2681-487D-9322-615EB35A29E6}"/>
   </bookViews>
   <sheets>
     <sheet name="09_RT-qPCR_data" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -159,7 +159,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
